--- a/data/trans_dic/P57_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P57_R-Clase-trans_dic.xlsx
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10)</t>
+          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10) (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,51; 17,43</t>
+          <t>10,2; 17,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,87; 15,29</t>
+          <t>8,85; 14,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,35; 15,19</t>
+          <t>8,07; 15,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,36; 10,66</t>
+          <t>6,39; 10,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,18; 15,29</t>
+          <t>10,19; 15,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,26; 12,06</t>
+          <t>8,31; 11,94</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,72; 15,84</t>
+          <t>9,18; 16,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,61; 13,09</t>
+          <t>7,4; 12,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,96; 18,78</t>
+          <t>11,19; 18,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,98; 15,62</t>
+          <t>9,78; 15,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,04; 16,22</t>
+          <t>11,2; 16,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,29; 13,18</t>
+          <t>9,32; 13,53</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,74; 25,99</t>
+          <t>18,82; 26,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,42; 15,94</t>
+          <t>3,57; 15,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,48; 38,53</t>
+          <t>22,57; 37,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,97; 23,87</t>
+          <t>14,94; 24,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,11; 28,09</t>
+          <t>21,15; 28,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,83; 16,8</t>
+          <t>5,17; 16,84</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,66; 21,45</t>
+          <t>16,59; 21,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,01; 17,1</t>
+          <t>12,68; 17,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,06; 23,7</t>
+          <t>17,92; 23,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,8; 12,71</t>
+          <t>5,32; 12,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,85; 21,29</t>
+          <t>17,83; 21,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,42; 14,21</t>
+          <t>8,83; 14,19</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,08; 31,33</t>
+          <t>23,88; 31,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,56; 23,78</t>
+          <t>16,25; 22,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28,31; 35,27</t>
+          <t>28,42; 34,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,45; 26,12</t>
+          <t>16,45; 25,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,08; 32,14</t>
+          <t>27,34; 32,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,37; 24,01</t>
+          <t>17,48; 24,05</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,83; 10,21</t>
+          <t>3,91; 9,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,05; 8,42</t>
+          <t>2,1; 8,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23,24; 29,09</t>
+          <t>23,23; 28,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20,03; 25,0</t>
+          <t>19,71; 25,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,73; 24,13</t>
+          <t>19,62; 24,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,0; 20,28</t>
+          <t>15,89; 20,3</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,23; 19,82</t>
+          <t>17,16; 19,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,59; 14,07</t>
+          <t>9,31; 13,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22,07; 25,02</t>
+          <t>22,23; 25,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,14; 17,56</t>
+          <t>12,97; 17,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,05; 22,08</t>
+          <t>20,12; 22,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,32; 15,49</t>
+          <t>12,43; 15,49</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10)</t>
+          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10) (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1344,32 +1344,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>44909; 74463</t>
+          <t>43562; 74125</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>44826; 77268</t>
+          <t>44703; 75657</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28796; 52431</t>
+          <t>27849; 53312</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28411; 47588</t>
+          <t>28538; 48483</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>78640; 118072</t>
+          <t>78683; 116953</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>78595; 114784</t>
+          <t>79124; 113597</t>
         </is>
       </c>
     </row>
@@ -1462,32 +1462,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32663; 59371</t>
+          <t>34390; 60629</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34347; 59120</t>
+          <t>33435; 57742</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40439; 69299</t>
+          <t>41281; 70041</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38018; 59491</t>
+          <t>37258; 59273</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>82145; 120623</t>
+          <t>83288; 122301</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>77315; 109769</t>
+          <t>77561; 112611</t>
         </is>
       </c>
     </row>
@@ -1580,32 +1580,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>97272; 134860</t>
+          <t>97669; 135287</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>22883; 106492</t>
+          <t>23857; 106528</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37003; 63416</t>
+          <t>37139; 62244</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24990; 39837</t>
+          <t>24941; 41101</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>144266; 192005</t>
+          <t>144598; 192091</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>40358; 140305</t>
+          <t>43200; 140656</t>
         </is>
       </c>
     </row>
@@ -1698,32 +1698,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>190804; 245739</t>
+          <t>190012; 241907</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>133842; 175930</t>
+          <t>130464; 175725</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>148945; 195505</t>
+          <t>147819; 194675</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46796; 123774</t>
+          <t>51853; 124199</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>351781; 419540</t>
+          <t>351264; 421983</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>168745; 284634</t>
+          <t>176795; 284256</t>
         </is>
       </c>
     </row>
@@ -1816,32 +1816,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>148955; 193784</t>
+          <t>147742; 192970</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>78237; 112389</t>
+          <t>76796; 108511</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>208373; 259591</t>
+          <t>209161; 257334</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>137750; 218698</t>
+          <t>137746; 216759</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>366763; 435389</t>
+          <t>370365; 439482</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>227482; 314446</t>
+          <t>228893; 314971</t>
         </is>
       </c>
     </row>
@@ -1934,32 +1934,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10984; 29330</t>
+          <t>11238; 28043</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4940; 20245</t>
+          <t>5042; 19999</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>249975; 312954</t>
+          <t>249904; 309138</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>150713; 188085</t>
+          <t>148336; 188545</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>268869; 328794</t>
+          <t>267399; 334925</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>158874; 201377</t>
+          <t>157777; 201585</t>
         </is>
       </c>
     </row>
@@ -2052,32 +2052,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>580897; 668331</t>
+          <t>578607; 671036</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>322986; 473933</t>
+          <t>313434; 470225</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>775630; 879517</t>
+          <t>781455; 881610</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>467667; 624734</t>
+          <t>461408; 618933</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1381153; 1521034</t>
+          <t>1385966; 1515342</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>853300; 1073062</t>
+          <t>860520; 1073061</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P57_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P57_R-Clase-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,2; 17,35</t>
+          <t>10,46; 17,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,85; 14,98</t>
+          <t>8,86; 14,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,07; 15,45</t>
+          <t>8,1; 15,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,39; 10,86</t>
+          <t>7,01; 11,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,19; 15,15</t>
+          <t>10,32; 15,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,31; 11,94</t>
+          <t>8,66; 12,51</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,18; 16,18</t>
+          <t>9,18; 16,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,4; 12,79</t>
+          <t>7,23; 12,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,19; 18,98</t>
+          <t>10,95; 18,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,78; 15,56</t>
+          <t>10,18; 15,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,2; 16,44</t>
+          <t>11,05; 16,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,32; 13,53</t>
+          <t>9,32; 13,02</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,82; 26,07</t>
+          <t>18,58; 26,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,57; 15,94</t>
+          <t>11,6; 17,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,57; 37,82</t>
+          <t>22,46; 38,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,94; 24,62</t>
+          <t>14,22; 23,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,15; 28,1</t>
+          <t>20,83; 27,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,17; 16,84</t>
+          <t>13,16; 18,3</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>13,61%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,59; 21,12</t>
+          <t>16,53; 21,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,68; 17,08</t>
+          <t>12,67; 16,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,92; 23,6</t>
+          <t>18,05; 23,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,32; 12,75</t>
+          <t>10,71; 14,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,83; 21,42</t>
+          <t>17,85; 21,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,83; 14,19</t>
+          <t>12,25; 15,09</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>22,96%</t>
         </is>
       </c>
     </row>
@@ -952,39 +952,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>23,88; 31,2</t>
+          <t>23,89; 30,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,25; 22,96</t>
+          <t>16,14; 22,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28,42; 34,96</t>
+          <t>28,19; 35,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,45; 25,89</t>
+          <t>23,39; 28,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,34; 32,44</t>
+          <t>27,09; 32,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,48; 24,05</t>
+          <t>20,88; 24,9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,91; 9,77</t>
+          <t>3,79; 9,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,1; 8,32</t>
+          <t>2,76; 9,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23,23; 28,74</t>
+          <t>23,4; 29,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19,71; 25,06</t>
+          <t>19,65; 24,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,62; 24,58</t>
+          <t>19,58; 24,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,89; 20,3</t>
+          <t>16,31; 20,39</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,16; 19,9</t>
+          <t>17,16; 19,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,31; 13,96</t>
+          <t>12,38; 14,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22,23; 25,08</t>
+          <t>22,04; 24,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,97; 17,39</t>
+          <t>16,49; 18,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,12; 22,0</t>
+          <t>20,03; 22,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,43; 15,49</t>
+          <t>14,76; 16,41</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>57132</t>
+          <t>62984</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37338</t>
+          <t>44437</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94470</t>
+          <t>107421</t>
         </is>
       </c>
     </row>
@@ -1344,32 +1344,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>43562; 74125</t>
+          <t>44693; 72962</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>44703; 75657</t>
+          <t>48776; 81388</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27849; 53312</t>
+          <t>27933; 53040</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28538; 48483</t>
+          <t>34138; 57276</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>78683; 116953</t>
+          <t>79703; 118100</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79124; 113597</t>
+          <t>89909; 129856</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>44695</t>
+          <t>46634</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47646</t>
+          <t>53235</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92341</t>
+          <t>99870</t>
         </is>
       </c>
     </row>
@@ -1462,32 +1462,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34390; 60629</t>
+          <t>34409; 60966</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33435; 57742</t>
+          <t>34898; 60811</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41281; 70041</t>
+          <t>40404; 69356</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37258; 59273</t>
+          <t>42894; 66272</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>83288; 122301</t>
+          <t>82209; 119236</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>77561; 112611</t>
+          <t>84263; 117711</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>63447</t>
+          <t>67837</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31846</t>
+          <t>34480</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95293</t>
+          <t>102317</t>
         </is>
       </c>
     </row>
@@ -1580,32 +1580,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>97669; 135287</t>
+          <t>96407; 136473</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23857; 106528</t>
+          <t>54716; 83715</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37139; 62244</t>
+          <t>36971; 64088</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24941; 41101</t>
+          <t>26663; 44096</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>144598; 192091</t>
+          <t>142387; 188750</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>43200; 140656</t>
+          <t>86762; 120598</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>153726</t>
+          <t>164057</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92399</t>
+          <t>105643</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>246124</t>
+          <t>269701</t>
         </is>
       </c>
     </row>
@@ -1698,32 +1698,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>190012; 241907</t>
+          <t>189400; 242555</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>130464; 175725</t>
+          <t>142627; 187864</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>147819; 194675</t>
+          <t>148887; 197706</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>51853; 124199</t>
+          <t>91722; 122141</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>351264; 421983</t>
+          <t>351767; 420466</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>176795; 284256</t>
+          <t>242779; 299042</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>92709</t>
+          <t>108700</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>187366</t>
+          <t>210884</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>280075</t>
+          <t>319583</t>
         </is>
       </c>
     </row>
@@ -1816,39 +1816,39 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>147742; 192970</t>
+          <t>147770; 191390</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>76796; 108511</t>
+          <t>91269; 127045</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>209161; 257334</t>
+          <t>207516; 260962</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>137746; 216759</t>
+          <t>193329; 232056</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>370365; 439482</t>
+          <t>367024; 434874</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>228893; 314971</t>
+          <t>290612; 346624</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>10583</t>
+          <t>12431</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>168823</t>
+          <t>183920</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>179406</t>
+          <t>196351</t>
         </is>
       </c>
     </row>
@@ -1934,32 +1934,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11238; 28043</t>
+          <t>10884; 28443</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5042; 19999</t>
+          <t>6542; 23361</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>249904; 309138</t>
+          <t>251712; 313822</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>148336; 188545</t>
+          <t>164217; 204713</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>267399; 334925</t>
+          <t>266872; 332766</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>157777; 201585</t>
+          <t>175012; 218862</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>422291</t>
+          <t>462644</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>565417</t>
+          <t>632599</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>987709</t>
+          <t>1095243</t>
         </is>
       </c>
     </row>
@@ -2052,32 +2052,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>578607; 671036</t>
+          <t>578718; 673678</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>313434; 470225</t>
+          <t>424870; 505602</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>781455; 881610</t>
+          <t>774897; 876973</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>461408; 618933</t>
+          <t>596176; 670618</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1385966; 1515342</t>
+          <t>1379794; 1521472</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>860520; 1073061</t>
+          <t>1040312; 1156487</t>
         </is>
       </c>
     </row>
